--- a/core/seed.xlsx
+++ b/core/seed.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\mint\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\projects\mint\core\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B6BF53-DF37-4361-8837-E2B31334645C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F97CBA-7704-4AD1-BC04-E0396897B482}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{B83D3B56-97C9-4CBC-877B-EED75B384087}"/>
+    <workbookView xWindow="38290" yWindow="-14330" windowWidth="21820" windowHeight="37900" activeTab="1" xr2:uid="{B83D3B56-97C9-4CBC-877B-EED75B384087}"/>
   </bookViews>
   <sheets>
     <sheet name="nodes" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="60">
   <si>
     <t>id</t>
   </si>
@@ -124,10 +124,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>id,named,commented,time_stamped,user_stamped,stash_stamped</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>项目分类1</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -211,6 +207,66 @@
   </si>
   <si>
     <t>type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>data_type</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>integer</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(128)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>varchar(512)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>datetime</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>foreign_key</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>is_primary</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>unique</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>onupdate</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ondelete</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>server_default</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nullable</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>non_named_supers,named</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>nick</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -575,7 +631,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7B405FA2-5FE9-4E88-A58E-E57B5833F7E2}">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3.1640625" bestFit="1" customWidth="1"/>
@@ -584,7 +640,7 @@
     <col min="4" max="4" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -598,13 +654,16 @@
         <v>15</v>
       </c>
       <c r="E1" t="s">
+        <v>30</v>
+      </c>
+      <c r="F1" t="s">
+        <v>44</v>
+      </c>
+      <c r="G1" t="s">
         <v>31</v>
       </c>
-      <c r="F1" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -618,7 +677,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -632,7 +691,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
@@ -646,7 +705,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>3</v>
       </c>
@@ -660,7 +719,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>4</v>
       </c>
@@ -674,7 +733,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>5</v>
       </c>
@@ -688,21 +747,21 @@
         <v>16</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>37</v>
       </c>
       <c r="F8" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>7</v>
       </c>
@@ -710,13 +769,13 @@
         <v>42</v>
       </c>
       <c r="C9" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="F9" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>8</v>
       </c>
@@ -724,10 +783,10 @@
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>9</v>
       </c>
@@ -735,10 +794,10 @@
         <v>4</v>
       </c>
       <c r="C11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>10</v>
       </c>
@@ -746,13 +805,13 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>11</v>
       </c>
@@ -760,13 +819,13 @@
         <v>11</v>
       </c>
       <c r="C13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>12</v>
       </c>
@@ -774,13 +833,13 @@
         <v>12</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>13</v>
       </c>
@@ -788,13 +847,13 @@
         <v>13</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D15" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>14</v>
       </c>
@@ -802,10 +861,10 @@
         <v>9</v>
       </c>
       <c r="C16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D16" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -816,10 +875,10 @@
         <v>10</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D17" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -830,14 +889,18 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3E362F47-2C2F-4B38-964B-27E8C249B8FB}">
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:N19"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="14.83203125" customWidth="1"/>
     <col min="3" max="3" width="13.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.9140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="10.9140625" customWidth="1"/>
+    <col min="9" max="9" width="12.08203125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -848,10 +911,40 @@
         <v>3</v>
       </c>
       <c r="D1" t="s">
+        <v>30</v>
+      </c>
+      <c r="E1" t="s">
+        <v>46</v>
+      </c>
+      <c r="F1" t="s">
+        <v>52</v>
+      </c>
+      <c r="G1" t="s">
+        <v>53</v>
+      </c>
+      <c r="H1" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" t="s">
+        <v>56</v>
+      </c>
+      <c r="J1" t="s">
+        <v>45</v>
+      </c>
+      <c r="K1" t="s">
+        <v>51</v>
+      </c>
+      <c r="L1" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>0</v>
       </c>
@@ -864,8 +957,17 @@
       <c r="D2">
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E2" t="s">
+        <v>47</v>
+      </c>
+      <c r="F2">
+        <v>1</v>
+      </c>
+      <c r="H2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>1</v>
       </c>
@@ -878,41 +980,62 @@
       <c r="D3">
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E3" t="s">
+        <v>48</v>
+      </c>
+      <c r="H3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C4" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4">
+        <v>1</v>
+      </c>
+      <c r="H4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="s">
+        <v>49</v>
+      </c>
+      <c r="H5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6" t="s">
         <v>32</v>
-      </c>
-      <c r="C4" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>4</v>
-      </c>
-      <c r="B6" t="s">
-        <v>34</v>
       </c>
       <c r="C6" t="s">
         <v>20</v>
@@ -920,172 +1043,279 @@
       <c r="D6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="E6" t="s">
+        <v>50</v>
+      </c>
+      <c r="H6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" t="s">
+        <v>20</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
+        <v>50</v>
+      </c>
+      <c r="H7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A8">
         <v>5</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B8" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="s">
+        <v>48</v>
+      </c>
+      <c r="H8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>6</v>
+      </c>
+      <c r="B9" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="s">
-        <v>21</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A8">
+      <c r="C9" t="s">
+        <v>22</v>
+      </c>
+      <c r="D9">
+        <v>0</v>
+      </c>
+      <c r="E9" t="s">
+        <v>50</v>
+      </c>
+      <c r="H9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>7</v>
+      </c>
+      <c r="B10" t="s">
         <v>6</v>
-      </c>
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>8</v>
-      </c>
-      <c r="B10" t="s">
-        <v>14</v>
       </c>
       <c r="C10" t="s">
         <v>5</v>
       </c>
       <c r="D10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E10" t="s">
+        <v>48</v>
+      </c>
+      <c r="H10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
         <v>5</v>
       </c>
       <c r="D11">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+        <v>1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>48</v>
+      </c>
+      <c r="H11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
         <v>5</v>
       </c>
       <c r="D12">
+        <v>2</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13">
         <v>3</v>
       </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A13">
+      <c r="E13" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A14">
         <v>11</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B14" t="s">
         <v>3</v>
-      </c>
-      <c r="C13" t="s">
-        <v>4</v>
-      </c>
-      <c r="D13">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A14">
-        <v>12</v>
-      </c>
-      <c r="B14" t="s">
-        <v>31</v>
       </c>
       <c r="C14" t="s">
         <v>4</v>
       </c>
       <c r="D14">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E14" t="s">
+        <v>48</v>
+      </c>
+      <c r="H14">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A15">
+        <v>12</v>
+      </c>
+      <c r="B15" t="s">
+        <v>30</v>
+      </c>
+      <c r="C15" t="s">
+        <v>4</v>
+      </c>
+      <c r="D15">
+        <v>1</v>
+      </c>
+      <c r="E15" t="s">
+        <v>48</v>
+      </c>
+      <c r="H15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="A16">
         <v>13</v>
       </c>
-      <c r="B15" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" t="s">
-        <v>8</v>
-      </c>
-      <c r="D15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A16">
-        <v>14</v>
-      </c>
       <c r="B16" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C16" t="s">
         <v>8</v>
       </c>
       <c r="D16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
+        <v>0</v>
+      </c>
+      <c r="E16" t="s">
+        <v>48</v>
+      </c>
+      <c r="H16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
+        <v>14</v>
+      </c>
+      <c r="B17" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17">
+        <v>1</v>
+      </c>
+      <c r="E17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A18">
         <v>15</v>
       </c>
-      <c r="B17" t="s">
+      <c r="B18" t="s">
+        <v>39</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>0</v>
+      </c>
+      <c r="E18" t="s">
+        <v>48</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>16</v>
+      </c>
+      <c r="B19" t="s">
         <v>40</v>
       </c>
-      <c r="C17" t="s">
-        <v>11</v>
-      </c>
-      <c r="D17">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
-      <c r="A18">
-        <v>16</v>
-      </c>
-      <c r="B18" t="s">
-        <v>41</v>
-      </c>
-      <c r="C18" t="s">
+      <c r="C19" t="s">
         <v>12</v>
       </c>
-      <c r="D18">
+      <c r="D19">
+        <v>0</v>
+      </c>
+      <c r="E19" t="s">
+        <v>48</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19">
         <v>0</v>
       </c>
     </row>
